--- a/Assets/Data/DataMichaelWorking.xlsx
+++ b/Assets/Data/DataMichaelWorking.xlsx
@@ -204,7 +204,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -270,6 +270,12 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -540,7 +546,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>

--- a/Assets/Data/DataMichaelWorking.xlsx
+++ b/Assets/Data/DataMichaelWorking.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Structure" sheetId="1" state="visible" r:id="rId3"/>
@@ -13,6 +13,7 @@
     <sheet name="Resources" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Rarity" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="ArmyGenerator" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="ShopGenerator" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">ArmyGenerator!$A$1:$F$15</definedName>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="61">
   <si>
     <t xml:space="preserve">Num Code</t>
   </si>
@@ -195,6 +196,61 @@
   </si>
   <si>
     <t xml:space="preserve">Unit 2 Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Common Weight</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Uncommon </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Weight</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rare </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Weight</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Forced Uncommon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forced Rare</t>
   </si>
 </sst>
 </file>
@@ -204,7 +260,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -276,6 +332,12 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -477,7 +539,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -560,6 +622,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2260,4 +2326,429 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultColWidth="12.8046875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17.29"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C15" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C17" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C19" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/Assets/Data/DataMichaelWorking.xlsx
+++ b/Assets/Data/DataMichaelWorking.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="96">
   <si>
     <t xml:space="preserve">Num Code</t>
   </si>
@@ -72,7 +72,205 @@
     <t xml:space="preserve">Output Value</t>
   </si>
   <si>
-    <t xml:space="preserve">knight-maker</t>
+    <t xml:space="preserve">Transaction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">garrison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Common</t>
+  </si>
+  <si>
+    <t xml:space="preserve">population</t>
+  </si>
+  <si>
+    <t xml:space="preserve">knight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:2|gems:1;output=mage:1|knight:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flechery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">archer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lancer-maker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cavalry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">giant-maker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">giant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assasins-guild</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assassin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">barracks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soldier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">god-maker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">god</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gunsmith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gunner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peasant-homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peasantry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peasant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mage-tower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon-nest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">egg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon-hatchery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gem-mine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon-rider-roost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uncommon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon-rider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">farm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pop-growth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold-mine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold-income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">granary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">treasury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunters-lodge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">this is a long sentence. I am testing if this breaks. We will see</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trading-post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mage-academy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bigger-mage-tower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">archmage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crystal-refinery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mage-university</t>
+  </si>
+  <si>
+    <t xml:space="preserve">work-house</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peasant-lodge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack Speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack Range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Move Speed</t>
   </si>
   <si>
     <t xml:space="preserve">Ipsem lorem description bullshit</t>
@@ -81,105 +279,12 @@
     <t xml:space="preserve">Ipsem lorem notes bullshit</t>
   </si>
   <si>
-    <t xml:space="preserve">structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Common</t>
-  </si>
-  <si>
-    <t xml:space="preserve">population</t>
-  </si>
-  <si>
-    <t xml:space="preserve">knight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">archer-maker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">archer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lancer-maker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lancer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cavalry-maker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cavalry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">giant-maker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">giant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assassin-maker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assassin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gunner-maker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gunner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peasant-maker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peasant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">god-maker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">god</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attack Speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attack Range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Move Speed</t>
-  </si>
-  <si>
     <t xml:space="preserve">unit</t>
   </si>
   <si>
     <t xml:space="preserve">gold</t>
   </si>
   <si>
-    <t xml:space="preserve">pop-growth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uncommon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rare</t>
-  </si>
-  <si>
     <t xml:space="preserve">ArmyID</t>
   </si>
   <si>
@@ -201,50 +306,10 @@
     <t xml:space="preserve">Common Weight</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Uncommon </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Weight</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Rare </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Weight</t>
-    </r>
+    <t xml:space="preserve">Uncommon Weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rare Weight</t>
   </si>
   <si>
     <t xml:space="preserve">Forced Uncommon</t>
@@ -260,7 +325,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -320,25 +385,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -539,7 +585,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -596,19 +642,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -616,15 +658,15 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1000,7 +1042,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.71"/>
@@ -1014,6 +1056,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="13.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="14.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="13.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="44.93"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1059,16 +1102,19 @@
       <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="0" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>16</v>
@@ -1103,16 +1149,19 @@
       <c r="N2" s="10" t="n">
         <v>4</v>
       </c>
+      <c r="O2" s="0" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>16</v>
@@ -1142,10 +1191,13 @@
         <v>2</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N3" s="10" t="n">
         <v>4</v>
+      </c>
+      <c r="O3" s="0" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1153,10 +1205,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>16</v>
@@ -1186,21 +1238,24 @@
         <v>2</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N4" s="10" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O4" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>16</v>
@@ -1230,10 +1285,13 @@
         <v>2</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N5" s="10" t="n">
         <v>4</v>
+      </c>
+      <c r="O5" s="0" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1241,10 +1299,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>16</v>
@@ -1274,10 +1332,13 @@
         <v>2</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N6" s="10" t="n">
         <v>1</v>
+      </c>
+      <c r="O6" s="0" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1285,10 +1346,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>16</v>
@@ -1318,21 +1379,24 @@
         <v>2</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N7" s="10" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O7" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>16</v>
@@ -1347,7 +1411,7 @@
         <v>19</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>20</v>
@@ -1362,21 +1426,24 @@
         <v>2</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N8" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>4</v>
+      </c>
+      <c r="O8" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>16</v>
@@ -1391,13 +1458,13 @@
         <v>19</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>20</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>20</v>
@@ -1406,10 +1473,13 @@
         <v>2</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N9" s="10" t="n">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="O9" s="0" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1417,10 +1487,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>16</v>
@@ -1435,7 +1505,7 @@
         <v>19</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="I10" s="9" t="s">
         <v>20</v>
@@ -1450,15 +1520,911 @@
         <v>2</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N10" s="10" t="n">
         <v>1</v>
+      </c>
+      <c r="O10" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="N11" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="N12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="J13" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="N13" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="N14" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="N15" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="N16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="N17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="N18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="N19" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="N20" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="N21" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="O21" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="L22" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="N22" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O22" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="L23" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="N23" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O23" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L24" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="N24" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O24" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="N25" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="N26" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O26" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="N27" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O27" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L28" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="N28" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="O28" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L29" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="N29" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="O29" s="0" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G2:G10" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G2:G29" type="list">
       <formula1>INDIRECT("RarityData")</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1516,25 +2482,25 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="M1" s="12" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1545,13 +2511,13 @@
         <v>21</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>18</v>
@@ -1581,16 +2547,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>18</v>
@@ -1620,16 +2586,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>18</v>
@@ -1659,16 +2625,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>18</v>
@@ -1698,16 +2664,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>18</v>
@@ -1737,16 +2703,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>18</v>
@@ -1776,16 +2742,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>18</v>
@@ -1815,16 +2781,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>18</v>
@@ -1854,16 +2820,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>18</v>
@@ -1930,10 +2896,10 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1946,10 +2912,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1989,12 +2955,12 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2021,297 +2987,297 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>55</v>
+        <v>88</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="0" t="n">
+      <c r="A2" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="17"/>
+      <c r="F2" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="19" t="s">
+      <c r="A3" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="20"/>
-      <c r="F3" s="0" t="n">
+      <c r="D3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="19"/>
+      <c r="F3" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="n">
+      <c r="A4" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="19" t="s">
+      <c r="B4" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="0" t="n">
+      <c r="D4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="0" t="n">
+      <c r="D5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="0" t="n">
+      <c r="E6" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="n">
+      <c r="A7" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="0" t="n">
+      <c r="E7" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="n">
+      <c r="A8" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="0" t="n">
+      <c r="E8" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="n">
+      <c r="A9" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="E9" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="0" t="n">
+      <c r="E9" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="n">
+      <c r="A10" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="E10" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="0" t="n">
+      <c r="E10" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16" t="n">
+      <c r="A11" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E11" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="0" t="n">
+      <c r="E11" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="n">
+      <c r="A12" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="E12" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="0" t="n">
+      <c r="E12" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="16" t="n">
+      <c r="A13" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="E13" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="0" t="n">
+      <c r="E13" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="n">
+      <c r="A14" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="0" t="n">
+      <c r="D14" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="E14" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="0" t="n">
+      <c r="E14" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="1" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="16" t="n">
+      <c r="A15" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="0" t="n">
+      <c r="D15" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="E15" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" s="0" t="n">
+      <c r="E15" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="1" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2336,409 +3302,409 @@
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="12.8046875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="0" t="n">
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="0" t="n">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="0" t="n">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="D4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="0" t="n">
+      <c r="D4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="0" t="n">
+      <c r="B5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="D5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="0" t="n">
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="0" t="n">
+      <c r="B6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="D6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="0" t="n">
+      <c r="D6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="0" t="n">
+      <c r="B7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="D7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="0" t="n">
+      <c r="D7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="0" t="n">
+      <c r="B8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="E8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="0" t="n">
+      <c r="E8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="21" t="n">
+      <c r="B9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="20" t="n">
         <v>0.6</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="E9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="0" t="n">
+      <c r="E9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="0" t="n">
+      <c r="B10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="E10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="0" t="n">
+      <c r="E10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="21" t="n">
+      <c r="B11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="20" t="n">
         <v>0.6</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="E11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="0" t="n">
+      <c r="E11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="0" t="n">
+      <c r="B12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="E12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="0" t="n">
+      <c r="E12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="0" t="n">
+      <c r="B13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="E13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="0" t="n">
+      <c r="E13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="0" t="n">
+      <c r="B14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="E14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="0" t="n">
+      <c r="E14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="C15" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="0" t="n">
+      <c r="C15" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="E15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="0" t="n">
+      <c r="E15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="21" t="n">
+      <c r="B16" s="20" t="n">
         <v>0.6</v>
       </c>
-      <c r="C16" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="0" t="n">
+      <c r="C16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="E16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="0" t="n">
+      <c r="E16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="C17" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="0" t="n">
+      <c r="C17" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="21" t="n">
+      <c r="B18" s="20" t="n">
         <v>0.6</v>
       </c>
-      <c r="C18" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="0" t="n">
+      <c r="C18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="C19" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="0" t="n">
+      <c r="C19" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+      <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="21" t="n">
+      <c r="B20" s="20" t="n">
         <v>0.6</v>
       </c>
-      <c r="C20" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="0" t="n">
+      <c r="C20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/DataMichaelWorking.xlsx
+++ b/Assets/Data/DataMichaelWorking.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="114">
   <si>
     <t xml:space="preserve">Num Code</t>
   </si>
@@ -54,24 +54,6 @@
     <t xml:space="preserve">Gold Cost</t>
   </si>
   <si>
-    <t xml:space="preserve">Resource 1 In</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input 1 Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource 2 In</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input 2 Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource Out</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Output Value</t>
-  </si>
-  <si>
     <t xml:space="preserve">Transaction</t>
   </si>
   <si>
@@ -90,199 +72,327 @@
     <t xml:space="preserve">Common</t>
   </si>
   <si>
+    <t xml:space="preserve">input=population:1;
+output=knight:4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flechery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1;
+output=archer:4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lancer-maker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1;
+output=lancer:4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1;
+output=cavalry:4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">giant-maker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1;
+output=giant:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assasins-guild</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1;
+output=assassin:2|gems:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">barracks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1;
+output=soldier:4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1|gems:1;
+output=druid:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gunsmith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1;
+output=gunner:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peasant-homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peasantry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:5;
+output=peasant:5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mage-tower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=gems:2;
+output=mage:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon-nest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=gems:2;
+output=egg:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon-hatchery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=egg:1;
+output=dragon:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gem-mine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1;
+output=gems:3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon-rider-roost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uncommon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=dragon:1;
+output=dragon-rider:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">farm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1;
+output=pop-growth:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold-mine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1;
+output=gold:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">granary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1;
+output=pop-growth:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">treasury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1;
+output=gold:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunters-lodge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">this is a long sentence. I am testing if this breaks. We will see</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:5;
+output=hunter:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1;
+output=pop-growth:3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trading-post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:3;
+output=gold:3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mage-academy</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">input=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">population:1|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">gems:1;
+output=mage:3</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">bigger-mage-tower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:3|gems:1;
+output=mage:3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crystal-refinery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:2;
+output=gems:5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mage-university</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=gems:3;
+output=archmage:3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">work-house</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:15;
+output=peasant:20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peasant-lodge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:20;
+output=peasant:30 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack Speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack Range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Move Speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">knight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description of the unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">notes about the unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">archer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cavalry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">giant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assassin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soldier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gunner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peasant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">druid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">debug tool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon-rider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">archmage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold</t>
+  </si>
+  <si>
     <t xml:space="preserve">population</t>
   </si>
   <si>
-    <t xml:space="preserve">knight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">input=population:2|gems:1;output=mage:1|knight:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flechery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">archer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lancer-maker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lancer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cavalry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">giant-maker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">giant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assasins-guild</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assassin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">barracks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soldier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">god-maker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">god</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gunsmith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gunner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peasant-homes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peasantry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peasant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mage-tower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon-nest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">egg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon-hatchery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gem-mine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon-rider-roost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uncommon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon-rider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">farm</t>
-  </si>
-  <si>
     <t xml:space="preserve">pop-growth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold-mine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold-income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">granary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">treasury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hunters-lodge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">this is a long sentence. I am testing if this breaks. We will see</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hunter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trading-post</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mage-academy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bigger-mage-tower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">archmage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crystal-refinery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mage-university</t>
-  </si>
-  <si>
-    <t xml:space="preserve">work-house</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peasant-lodge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attack Speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attack Range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Move Speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ipsem lorem description bullshit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ipsem lorem notes bullshit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold</t>
   </si>
   <si>
     <t xml:space="preserve">ArmyID</t>
@@ -325,7 +435,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -369,6 +479,12 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -560,7 +676,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -584,8 +700,11 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -622,12 +741,20 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -638,11 +765,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -671,13 +798,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="data" xfId="20"/>
   </cellStyles>
   <dxfs count="7">
     <dxf>
@@ -834,12 +962,12 @@
     <tableColumn id="6" name="Archetype"/>
     <tableColumn id="7" name="Rarity"/>
     <tableColumn id="8" name="Gold Cost"/>
-    <tableColumn id="9" name="Resource 1 In"/>
-    <tableColumn id="10" name="Input 1 Value"/>
-    <tableColumn id="11" name="Resource 2 In"/>
-    <tableColumn id="12" name="Input 2 Value"/>
-    <tableColumn id="13" name="Resource Out"/>
-    <tableColumn id="14" name="Output Value"/>
+    <tableColumn id="9" name="Transaction"/>
+    <tableColumn id="10" name=""/>
+    <tableColumn id="11" name=""/>
+    <tableColumn id="12" name=""/>
+    <tableColumn id="13" name=""/>
+    <tableColumn id="14" name=""/>
   </tableColumns>
 </table>
 </file>
@@ -854,13 +982,13 @@
     <tableColumn id="4" name="Notes"/>
     <tableColumn id="5" name="Sprite"/>
     <tableColumn id="6" name="Archetype"/>
-    <tableColumn id="7" name="Structure"/>
-    <tableColumn id="8" name="Size"/>
-    <tableColumn id="9" name="Health"/>
-    <tableColumn id="10" name="Attack"/>
-    <tableColumn id="11" name="Attack Speed"/>
-    <tableColumn id="12" name="Attack Range"/>
-    <tableColumn id="13" name="Move Speed"/>
+    <tableColumn id="7" name="Size"/>
+    <tableColumn id="8" name="Health"/>
+    <tableColumn id="9" name="Attack"/>
+    <tableColumn id="10" name="Attack Speed"/>
+    <tableColumn id="11" name="Attack Range"/>
+    <tableColumn id="12" name="Move Speed"/>
+    <tableColumn id="13" name=""/>
   </tableColumns>
 </table>
 </file>
@@ -1051,12 +1179,14 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="24.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="14.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="13.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="14.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="13.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="44.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="29.8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1087,187 +1217,138 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="5"/>
+    </row>
+    <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="3" t="s">
+      <c r="C2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="F2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="G2" s="7" t="s">
         <v>13</v>
-      </c>
-      <c r="O1" s="0" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="H2" s="8" t="n">
         <v>3</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="O2" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="J2" s="8"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="12"/>
+    </row>
+    <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H3" s="8" t="n">
         <v>3</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="O3" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>16</v>
+      </c>
+      <c r="J3" s="8"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="12"/>
+    </row>
+    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H4" s="8" t="n">
         <v>3</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L4" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="J4" s="8"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="12"/>
+    </row>
+    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="O4" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="n">
-        <v>4</v>
-      </c>
       <c r="B5" s="7" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H5" s="8" t="n">
         <v>5</v>
@@ -1275,1108 +1356,820 @@
       <c r="I5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N5" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="O5" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J5" s="8"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="12"/>
+    </row>
+    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>6</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L6" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N6" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" s="0" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="n">
+      <c r="J6" s="8"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>4</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L7" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="N7" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O7" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>24</v>
+      </c>
+      <c r="J7" s="8"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="12"/>
+    </row>
+    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>2</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L8" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="N8" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="J8" s="8"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="12"/>
+    </row>
+    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="O8" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>1000</v>
-      </c>
       <c r="I9" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L9" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="N9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>28</v>
+      </c>
+      <c r="J9" s="8"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="12"/>
+    </row>
+    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>7</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L10" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="N10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="J10" s="8"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="12"/>
+    </row>
+    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H11" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="N11" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="O11" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>33</v>
+      </c>
+      <c r="J11" s="8"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="12"/>
+    </row>
+    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>5</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="J12" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L12" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="N12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="J12" s="8"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="12"/>
+    </row>
+    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>2</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="J13" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L13" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="N13" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>39</v>
+      </c>
+      <c r="J13" s="8"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="12"/>
+    </row>
+    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="J14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="N14" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="n">
+        <v>41</v>
+      </c>
+      <c r="J14" s="8"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="12"/>
+    </row>
+    <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="n">
         <v>15</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J15" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="N15" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O15" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>43</v>
+      </c>
+      <c r="J15" s="8"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="12"/>
+    </row>
+    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="n">
         <v>16</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J16" s="8"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="12"/>
+    </row>
+    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="B17" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="J16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="N16" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>55</v>
-      </c>
       <c r="C17" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H17" s="8" t="n">
         <v>2</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="N17" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>48</v>
+      </c>
+      <c r="J17" s="8"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="12"/>
+    </row>
+    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="n">
         <v>18</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G18" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J18" s="8"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="12"/>
+    </row>
+    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="H18" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J18" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="N18" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="n">
-        <v>19</v>
-      </c>
       <c r="B19" s="7" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="H19" s="8" t="n">
         <v>3</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L19" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="N19" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O19" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>52</v>
+      </c>
+      <c r="J19" s="8"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="12"/>
+    </row>
+    <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="n">
         <v>20</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>4</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L20" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="N20" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O20" s="0" t="s">
-        <v>22</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="J20" s="8"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="n">
+      <c r="A21" s="13" t="n">
         <v>21</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J21" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="N21" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="O21" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>57</v>
+      </c>
+      <c r="J21" s="8"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="12"/>
+    </row>
+    <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="n">
         <v>22</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>7</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J22" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L22" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="J22" s="8"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="12"/>
+    </row>
+    <row r="23" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H23" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="M22" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="N22" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="O22" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>8</v>
-      </c>
       <c r="I23" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J23" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L23" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M23" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="N23" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="O23" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>62</v>
+      </c>
+      <c r="J23" s="8"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="12"/>
+    </row>
+    <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="n">
         <v>24</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>6</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="J24" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L24" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M24" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J24" s="8"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="12"/>
+    </row>
+    <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G25" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="N24" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="O24" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>53</v>
       </c>
       <c r="H25" s="8" t="n">
         <v>6</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="J25" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L25" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="N25" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>66</v>
+      </c>
+      <c r="J25" s="8"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="12"/>
+    </row>
+    <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="n">
         <v>26</v>
       </c>
       <c r="B26" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="J26" s="8"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="12"/>
+    </row>
+    <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I27" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="H26" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J26" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K26" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L26" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="N26" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="O26" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H27" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="J27" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K27" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L27" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M27" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="N27" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="O27" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J27" s="8"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="12"/>
+    </row>
+    <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="n">
         <v>28</v>
       </c>
       <c r="B28" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="H28" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J28" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L28" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M28" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="N28" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="O28" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11" t="n">
+      <c r="J28" s="8"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="12"/>
+    </row>
+    <row r="29" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="13" t="n">
         <v>29</v>
       </c>
       <c r="B29" s="7" t="s">
@@ -2386,41 +2179,29 @@
         <v>2</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J29" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="K29" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L29" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M29" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="N29" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="O29" s="0" t="s">
-        <v>22</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="J29" s="8"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="12"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2447,10 +2228,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="25.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.57"/>
@@ -2482,385 +2264,611 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="L1" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="L1" s="14" t="s">
         <v>80</v>
       </c>
+      <c r="M1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="C2" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="F2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K2" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L2" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="J2" s="7" t="n">
+      <c r="E3" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="K2" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" s="7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M2" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="7" t="n">
-        <v>10</v>
-      </c>
       <c r="J3" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M3" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="M3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L4" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="J4" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M4" s="7" t="n">
+      <c r="E5" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="7" t="n">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="J5" s="7" t="n">
+      <c r="L5" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="K5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M5" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="M5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="I6" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" s="7" t="s">
+      <c r="J6" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="J6" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L6" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M6" s="7" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="n">
+      <c r="E7" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" s="7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M7" s="7" t="n">
-        <v>6</v>
-      </c>
+      <c r="M7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M8" s="6"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="J8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="7"/>
+      <c r="G9" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="H9" s="7" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="L9" s="7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M9" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="M9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M10" s="6"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="D11" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J10" s="7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K10" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="L10" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M10" s="7" t="n">
-        <v>2</v>
-      </c>
+      <c r="E11" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="13"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="6"/>
+    </row>
+    <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" s="13"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="6"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" s="7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="13"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G2:G10" type="list">
-      <formula1>INDIRECT("StructureData[Name]")</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2887,35 +2895,35 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="13" t="s">
+      <c r="A1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>56</v>
+        <v>102</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>56</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -2944,23 +2952,23 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2986,296 +2994,296 @@
   <sheetFormatPr defaultColWidth="12.8046875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>90</v>
+      <c r="A1" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>41</v>
+      <c r="A2" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>92</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="17"/>
+      <c r="E2" s="19"/>
       <c r="F2" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>21</v>
+      <c r="A3" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>81</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="19"/>
+      <c r="E3" s="21"/>
       <c r="F3" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="15" t="n">
+      <c r="A4" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>21</v>
+      <c r="B4" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>81</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="19" t="s">
-        <v>24</v>
+      <c r="E4" s="21" t="s">
+        <v>84</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="n">
+      <c r="A5" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="15" t="n">
+      <c r="B5" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>21</v>
+      <c r="C5" s="20" t="s">
+        <v>81</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="19" t="s">
-        <v>24</v>
+      <c r="E5" s="21" t="s">
+        <v>84</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="n">
+      <c r="A6" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>21</v>
+      <c r="C6" s="20" t="s">
+        <v>81</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="19" t="s">
-        <v>24</v>
+      <c r="E6" s="21" t="s">
+        <v>84</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="n">
+      <c r="A7" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>21</v>
+      <c r="C7" s="20" t="s">
+        <v>81</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="19" t="s">
-        <v>24</v>
+      <c r="E7" s="21" t="s">
+        <v>84</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>21</v>
+      <c r="C8" s="20" t="s">
+        <v>81</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="19" t="s">
-        <v>24</v>
+      <c r="E8" s="21" t="s">
+        <v>84</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="n">
+      <c r="A9" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="18" t="s">
-        <v>21</v>
+      <c r="C9" s="20" t="s">
+        <v>81</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="E9" s="19" t="s">
-        <v>24</v>
+      <c r="E9" s="21" t="s">
+        <v>84</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="n">
+      <c r="A10" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="15" t="n">
+      <c r="B10" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="18" t="s">
-        <v>21</v>
+      <c r="C10" s="20" t="s">
+        <v>81</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="E10" s="19" t="s">
-        <v>24</v>
+      <c r="E10" s="21" t="s">
+        <v>84</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="15" t="n">
+      <c r="A11" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="18" t="s">
-        <v>21</v>
+      <c r="C11" s="20" t="s">
+        <v>81</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E11" s="19" t="s">
-        <v>24</v>
+      <c r="E11" s="21" t="s">
+        <v>84</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="n">
+      <c r="A12" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>21</v>
+      <c r="B12" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>81</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="E12" s="19" t="s">
-        <v>24</v>
+      <c r="E12" s="21" t="s">
+        <v>84</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="n">
+      <c r="A13" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="15" t="n">
+      <c r="B13" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="18" t="s">
-        <v>21</v>
+      <c r="C13" s="20" t="s">
+        <v>81</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="E13" s="19" t="s">
-        <v>24</v>
+      <c r="E13" s="21" t="s">
+        <v>84</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="n">
+      <c r="A14" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="15" t="n">
+      <c r="B14" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="18" t="s">
-        <v>21</v>
+      <c r="C14" s="20" t="s">
+        <v>81</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="E14" s="19" t="s">
-        <v>24</v>
+      <c r="E14" s="21" t="s">
+        <v>84</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="15" t="n">
+      <c r="A15" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="15" t="n">
+      <c r="B15" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="18" t="s">
-        <v>21</v>
+      <c r="C15" s="20" t="s">
+        <v>81</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="E15" s="19" t="s">
-        <v>24</v>
+      <c r="E15" s="21" t="s">
+        <v>84</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>8</v>
@@ -3309,23 +3317,23 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>95</v>
+      <c r="A1" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3475,7 +3483,7 @@
       <c r="B9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="22" t="n">
         <v>0.6</v>
       </c>
       <c r="D9" s="1" t="n">
@@ -3515,7 +3523,7 @@
       <c r="B11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="22" t="n">
         <v>0.6</v>
       </c>
       <c r="D11" s="1" t="n">
@@ -3555,7 +3563,7 @@
       <c r="B13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="1" t="n">
@@ -3595,7 +3603,7 @@
       <c r="B15" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="C15" s="20" t="n">
+      <c r="C15" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="1" t="n">
@@ -3612,7 +3620,7 @@
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="20" t="n">
+      <c r="B16" s="22" t="n">
         <v>0.6</v>
       </c>
       <c r="C16" s="1" t="n">
@@ -3635,7 +3643,7 @@
       <c r="B17" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="C17" s="20" t="n">
+      <c r="C17" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D17" s="1" t="n">
@@ -3652,7 +3660,7 @@
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="20" t="n">
+      <c r="B18" s="22" t="n">
         <v>0.6</v>
       </c>
       <c r="C18" s="1" t="n">
@@ -3675,7 +3683,7 @@
       <c r="B19" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="C19" s="20" t="n">
+      <c r="C19" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="1" t="n">
@@ -3692,7 +3700,7 @@
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="20" t="n">
+      <c r="B20" s="22" t="n">
         <v>0.6</v>
       </c>
       <c r="C20" s="1" t="n">

--- a/Assets/Data/DataMichaelWorking.xlsx
+++ b/Assets/Data/DataMichaelWorking.xlsx
@@ -73,7 +73,7 @@
   </si>
   <si>
     <t xml:space="preserve">input=population:1;
-output=knight:4</t>
+output=knight:4;</t>
   </si>
   <si>
     <t xml:space="preserve">flechery</t>
@@ -1223,7 +1223,7 @@
       <c r="M1" s="3"/>
       <c r="N1" s="5"/>
     </row>
-    <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="27.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="n">
         <v>1</v>
       </c>

--- a/Assets/Data/DataMichaelWorking.xlsx
+++ b/Assets/Data/DataMichaelWorking.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Structure" sheetId="1" state="visible" r:id="rId3"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="119">
   <si>
     <t xml:space="preserve">Num Code</t>
   </si>
@@ -244,36 +244,8 @@
     <t xml:space="preserve">mage-academy</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">input=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">population:1|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">gems:1;
+    <t xml:space="preserve">input=population:1|gems:1;
 output=mage:3</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">bigger-mage-tower</t>
@@ -329,6 +301,12 @@
     <t xml:space="preserve">Move Speed</t>
   </si>
   <si>
+    <t xml:space="preserve">Attack Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack Data</t>
+  </si>
+  <si>
     <t xml:space="preserve">knight</t>
   </si>
   <si>
@@ -338,9 +316,19 @@
     <t xml:space="preserve">notes about the unit</t>
   </si>
   <si>
+    <t xml:space="preserve">Melee</t>
+  </si>
+  <si>
     <t xml:space="preserve">archer</t>
   </si>
   <si>
+    <t xml:space="preserve">Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projectile-speed=3;
+projectile-sprite=arrow</t>
+  </si>
+  <si>
     <t xml:space="preserve">lancer</t>
   </si>
   <si>
@@ -368,10 +356,11 @@
     <t xml:space="preserve">druid</t>
   </si>
   <si>
-    <t xml:space="preserve">debug tool</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projectile-speed=3;
+projectile-sprite=magic-blast</t>
   </si>
   <si>
     <t xml:space="preserve">dragon-rider</t>
@@ -435,7 +424,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -481,10 +470,17 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Roboto"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -704,7 +700,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -741,7 +737,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -753,7 +749,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -765,11 +761,43 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -988,7 +1016,7 @@
     <tableColumn id="10" name="Attack Speed"/>
     <tableColumn id="11" name="Attack Range"/>
     <tableColumn id="12" name="Move Speed"/>
-    <tableColumn id="13" name=""/>
+    <tableColumn id="13" name="Attack Type"/>
   </tableColumns>
 </table>
 </file>
@@ -1179,7 +1207,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="24.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="14.43"/>
@@ -1223,7 +1251,7 @@
       <c r="M1" s="3"/>
       <c r="N1" s="5"/>
     </row>
-    <row r="2" customFormat="false" ht="27.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="n">
         <v>1</v>
       </c>
@@ -2228,11 +2256,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="25.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.57"/>
@@ -2241,10 +2269,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="16.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="14.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="14.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="25.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="38.47"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2281,23 +2310,28 @@
       <c r="L1" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="M1" s="2"/>
+      <c r="M1" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D2" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>83</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>81</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>12</v>
@@ -2320,23 +2354,26 @@
       <c r="L2" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="M2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M2" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="N2" s="15"/>
+    </row>
+    <row r="3" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>82</v>
-      </c>
       <c r="D3" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>12</v>
@@ -2359,23 +2396,28 @@
       <c r="L3" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M3" s="13"/>
+      <c r="M3" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="N3" s="16" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>83</v>
-      </c>
       <c r="E4" s="7" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>12</v>
@@ -2398,23 +2440,26 @@
       <c r="L4" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="M4" s="6"/>
+      <c r="M4" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="N4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>12</v>
@@ -2437,23 +2482,26 @@
       <c r="L5" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="M5" s="13"/>
+      <c r="M5" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="N5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>12</v>
@@ -2476,23 +2524,26 @@
       <c r="L6" s="7" t="n">
         <v>0.2</v>
       </c>
-      <c r="M6" s="6"/>
+      <c r="M6" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="N6" s="15"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>12</v>
@@ -2515,23 +2566,26 @@
       <c r="L7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="M7" s="13"/>
+      <c r="M7" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="N7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>12</v>
@@ -2554,23 +2608,26 @@
       <c r="L8" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="M8" s="6"/>
+      <c r="M8" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="N8" s="15"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>38</v>
@@ -2593,23 +2650,26 @@
       <c r="L9" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="M9" s="13"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M9" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="N9" s="16"/>
+    </row>
+    <row r="10" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>12</v>
@@ -2632,23 +2692,28 @@
       <c r="L10" s="7" t="n">
         <v>0.5</v>
       </c>
-      <c r="M10" s="6"/>
+      <c r="M10" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="N10" s="19" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>32</v>
@@ -2671,26 +2736,29 @@
       <c r="L11" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M11" s="13"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M11" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="N11" s="20"/>
+    </row>
+    <row r="12" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>1</v>
@@ -2710,23 +2778,28 @@
       <c r="L12" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M12" s="6"/>
+      <c r="M12" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="N12" s="19" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>38</v>
@@ -2749,23 +2822,26 @@
       <c r="L13" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="M13" s="13"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M13" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="N13" s="16"/>
+    </row>
+    <row r="14" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>35</v>
@@ -2788,23 +2864,28 @@
       <c r="L14" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M14" s="6"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M14" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="N14" s="19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>32</v>
@@ -2827,23 +2908,28 @@
       <c r="L15" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M15" s="13"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M15" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="N15" s="22" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>35</v>
@@ -2866,7 +2952,15 @@
       <c r="L16" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M16" s="6"/>
+      <c r="M16" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="N16" s="19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N17" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2895,35 +2989,35 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="15" t="s">
+      <c r="A1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="23" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -2952,7 +3046,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="23" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2994,296 +3088,296 @@
   <sheetFormatPr defaultColWidth="12.8046875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="F1" s="16" t="s">
+      <c r="A1" s="24" t="s">
         <v>108</v>
       </c>
+      <c r="B1" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>92</v>
+      <c r="A2" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>97</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="19"/>
+      <c r="E2" s="27"/>
       <c r="F2" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>81</v>
+      <c r="A3" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>83</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="21"/>
+      <c r="E3" s="29"/>
       <c r="F3" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="n">
+      <c r="A4" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>81</v>
+      <c r="B4" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>83</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="21" t="s">
-        <v>84</v>
+      <c r="E4" s="29" t="s">
+        <v>87</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="n">
+      <c r="A5" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="20" t="s">
-        <v>81</v>
+      <c r="C5" s="28" t="s">
+        <v>83</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="21" t="s">
-        <v>84</v>
+      <c r="E5" s="29" t="s">
+        <v>87</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="n">
+      <c r="A6" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="20" t="s">
-        <v>81</v>
+      <c r="C6" s="28" t="s">
+        <v>83</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="21" t="s">
-        <v>84</v>
+      <c r="E6" s="29" t="s">
+        <v>87</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="n">
+      <c r="A7" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="20" t="s">
-        <v>81</v>
+      <c r="C7" s="28" t="s">
+        <v>83</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="21" t="s">
-        <v>84</v>
+      <c r="E7" s="29" t="s">
+        <v>87</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="n">
+      <c r="A8" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="20" t="s">
-        <v>81</v>
+      <c r="C8" s="28" t="s">
+        <v>83</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="21" t="s">
-        <v>84</v>
+      <c r="E8" s="29" t="s">
+        <v>87</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="n">
+      <c r="A9" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="20" t="s">
-        <v>81</v>
+      <c r="C9" s="28" t="s">
+        <v>83</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="E9" s="21" t="s">
-        <v>84</v>
+      <c r="E9" s="29" t="s">
+        <v>87</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="n">
+      <c r="A10" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="20" t="s">
-        <v>81</v>
+      <c r="C10" s="28" t="s">
+        <v>83</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="E10" s="21" t="s">
-        <v>84</v>
+      <c r="E10" s="29" t="s">
+        <v>87</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="17" t="n">
+      <c r="A11" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="20" t="s">
-        <v>81</v>
+      <c r="C11" s="28" t="s">
+        <v>83</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E11" s="21" t="s">
-        <v>84</v>
+      <c r="E11" s="29" t="s">
+        <v>87</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="n">
+      <c r="A12" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>81</v>
+      <c r="B12" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>83</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="E12" s="21" t="s">
-        <v>84</v>
+      <c r="E12" s="29" t="s">
+        <v>87</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="17" t="n">
+      <c r="A13" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="17" t="n">
+      <c r="B13" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="20" t="s">
-        <v>81</v>
+      <c r="C13" s="28" t="s">
+        <v>83</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="E13" s="21" t="s">
-        <v>84</v>
+      <c r="E13" s="29" t="s">
+        <v>87</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="n">
+      <c r="A14" s="25" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B14" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="20" t="s">
-        <v>81</v>
+      <c r="C14" s="28" t="s">
+        <v>83</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="E14" s="21" t="s">
-        <v>84</v>
+      <c r="E14" s="29" t="s">
+        <v>87</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="17" t="n">
+      <c r="A15" s="25" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="17" t="n">
+      <c r="B15" s="25" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="20" t="s">
-        <v>81</v>
+      <c r="C15" s="28" t="s">
+        <v>83</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="E15" s="21" t="s">
-        <v>84</v>
+      <c r="E15" s="29" t="s">
+        <v>87</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>8</v>
@@ -3317,23 +3411,23 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="B1" s="16" t="s">
+      <c r="A1" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="C1" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>113</v>
+      <c r="B1" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3483,7 +3577,7 @@
       <c r="B9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C9" s="30" t="n">
         <v>0.6</v>
       </c>
       <c r="D9" s="1" t="n">
@@ -3523,7 +3617,7 @@
       <c r="B11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="30" t="n">
         <v>0.6</v>
       </c>
       <c r="D11" s="1" t="n">
@@ -3563,7 +3657,7 @@
       <c r="B13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="30" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="1" t="n">
@@ -3603,7 +3697,7 @@
       <c r="B15" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="30" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="1" t="n">
@@ -3620,7 +3714,7 @@
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="22" t="n">
+      <c r="B16" s="30" t="n">
         <v>0.6</v>
       </c>
       <c r="C16" s="1" t="n">
@@ -3643,7 +3737,7 @@
       <c r="B17" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="C17" s="22" t="n">
+      <c r="C17" s="30" t="n">
         <v>1</v>
       </c>
       <c r="D17" s="1" t="n">
@@ -3660,7 +3754,7 @@
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="22" t="n">
+      <c r="B18" s="30" t="n">
         <v>0.6</v>
       </c>
       <c r="C18" s="1" t="n">
@@ -3683,7 +3777,7 @@
       <c r="B19" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="C19" s="22" t="n">
+      <c r="C19" s="30" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="1" t="n">
@@ -3700,7 +3794,7 @@
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="22" t="n">
+      <c r="B20" s="30" t="n">
         <v>0.6</v>
       </c>
       <c r="C20" s="1" t="n">
